--- a/260726.xlsx
+++ b/260726.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99960BF6-A24A-45B7-9BD9-D22B3866332E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED43506-FFCD-4278-8121-FD25927A7FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="460" yWindow="4110" windowWidth="23470" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7020" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId3"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>每周采访-160731-Generalbundesanwalt</t>
   </si>
@@ -238,19 +237,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Geers: Sind das die Themen, mit denen die SPD auch in den Wahlkampf ziehen will?
-""""""""""""""""""""" Gabriel: Das sind erst mal die Themen, von denen ich den Eindruck habe, dass sie viele Menschen von allen Parteien erwarten und dass wir darüber reden müssen.
-Ich bin übrigens auch nicht dafür, dass wir einen überbordenden Staat bekommen.
-Ich bin eingeschult in eine neue Grundschule,  dann in ein neues Gymnasium, ich konnte richtig anfassen, dass Bildung was wert ist, die sanitären Anlagen in den Schulen waren besser als bei uns zu Hause.
-Und heute haben wir einen riesigen Sanierungsstau in unseren Bildungseinrichtungen.
-die besten Schulen stehen müssen, das müssen Leuchttürme sein.
-Nicht die Banktürme sind die Kathedralen unseres Landes, sondern die Schulgebäude.
-Und man kann nicht immer den Eltern sagen: Nehmt einen Eimer Farbe in die Hand und macht es selber – damit ist es nicht getan, wir brauchen auch Lehrer, Sozialarbeiter.
-Da zu investieren, das ist ja nichts, wo ein Mensch, der das von der Politik fordert, jetzt was irgendwie Unbotmäßiges oder nicht Bezahlbares fordern würde, das sind ganz normale Dinge.
-Dass man, wenn man arbeitet, anständige Geld verdient, </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ACEA oder aber auch andere Verbände in den USA. Es ist auch ein klassisches Feld, wo eben es noch keine neuen Rahmenbedingungen gibt, wo wir sehr, sehr gut in transatlantischen Verhältnissen Rahmenbedingungen entwickeln könnten, die dann sowohl in den USA als auch in Europa gelten können.
 Und wir müssten dann bei den Produkten eben auch keine unterschiedlichen Umsetzungen machen.
 Und das würde natürlich das Ganze auch erleichtern.
@@ -353,15 +339,6 @@
 Das ist auch ein wichtiger Unterschied, der zu machen ist.
 Hahne: Herr Mattes, vielen Dank für das Gespräch.
 Mattes: Bitteschön.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Deswegen müssen wir und auch die Insassen bewegen und es ist nicht notwendig, dass Fahrerinnen oder Fahrer tatsächlich eingreifen.
-Da braucht man ja einheitliche Standards, damit die Systeme auch kommunizieren können, damit es nicht zu Unfällen kommt.
-Wie kann das gelingen, wenn jeder Hersteller erstmal sein eigenes Süppchen kocht?
-Wie arbeiten Sie da zusammen?
-Mattes: mit der Politik und den rahmensetzenden Gremien, hinausgeht.
-Hier sind die Verbände gefordert</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -681,6 +658,24 @@
 Online-Ausgabe der  an Sie appelliert, systematisch und strukturiert auch insbesondere Folter durch die Assad-Seite in den Blick zu nehmen.
 Die Bundesanwaltschaft ist seit dem Inkrafttreten des Rom-Statuts ja mit der Umsetzung und mit der Verfolgung von Straftaten nach dem Völkerstrafgesetzbuch – das zeitgleich in Kraft getreten ist – beauftragt.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auch in den Wahlkampf ziehen will</t>
+  </si>
+  <si>
+    <t>Ich bin übrigens auch nicht dafür</t>
+  </si>
+  <si>
+    <t>besser als bei uns</t>
+  </si>
+  <si>
+    <t>Sanierungsstau</t>
+  </si>
+  <si>
+    <t>Unbotmäßiges</t>
+  </si>
+  <si>
+    <t>Deswegen müssen wir</t>
   </si>
 </sst>
 </file>
@@ -1008,15 +1003,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E0FF61-1578-4139-819D-7DBEAF65C891}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1026,25 +1046,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5908D9-E103-4C0C-AD88-EA8F5CA34567}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="34.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="210" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5843E79E-B574-48B8-8963-C7A72A603591}">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -1054,27 +1055,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="42" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1083,7 +1084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE0064EE-36F7-4A62-BA9D-3386994A50F9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -1093,7 +1094,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1102,7 +1103,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -1128,12 +1129,12 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -1142,10 +1143,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
